--- a/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
@@ -30,6 +30,12 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -39,11 +45,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>序号</t>
+      <t>模具编码</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -53,11 +65,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>模具编码</t>
+      <t>策略状态</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -67,11 +85,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>策略状态</t>
+      <t>返还标准</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -81,11 +105,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>返还标准</t>
+      <t>开始日期</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -95,11 +125,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>开始日期</t>
+      <t>结束日期</t>
     </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -109,25 +145,17 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>结束日期</t>
+      <t>返还数量上限</t>
     </r>
   </si>
   <si>
     <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>返还数量上限</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -142,6 +170,9 @@
   </si>
   <si>
     <t>备注</t>
+  </si>
+  <si>
+    <t>明细备注</t>
   </si>
 </sst>
 </file>
@@ -175,6 +206,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -317,12 +354,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -645,137 +676,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -783,6 +814,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1099,17 +1133,16 @@
   <dimension ref="A1:I1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.625" customWidth="1"/>
-    <col min="2" max="2" width="28.125" customWidth="1"/>
-    <col min="3" max="3" width="19.25" customWidth="1"/>
-    <col min="4" max="4" width="16.75" customWidth="1"/>
-    <col min="5" max="5" width="17.875" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="17.875" customWidth="1"/>
-    <col min="8" max="8" width="20.125" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="18.125" customWidth="1"/>
+    <col min="1" max="1" width="28.125" customWidth="1"/>
+    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="3" max="3" width="16.75" customWidth="1"/>
+    <col min="4" max="4" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="17.875" customWidth="1"/>
+    <col min="7" max="7" width="20.125" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="15" customWidth="1"/>
+    <col min="10" max="10" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1134,19 +1167,19 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B$1:B$1048576">
       <formula1>"启用,禁用"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D$1:D$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C$1:C$1048576">
       <formula1>"以采购下单数量,以采购收货数量,以采购入库数量"</formula1>
     </dataValidation>
   </dataValidations>

--- a/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
@@ -89,44 +89,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>开始日期</t>
-    </r>
+    <t>开始日期</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF333333"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>结束日期</t>
-    </r>
+    <t>结束日期</t>
   </si>
   <si>
     <r>
@@ -200,15 +166,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9.75"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1155,10 +1121,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1167,10 +1133,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
     </row>

--- a/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
@@ -89,10 +89,32 @@
     </r>
   </si>
   <si>
-    <t>开始日期</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>开始日期</t>
+    </r>
   </si>
   <si>
-    <t>结束日期</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF333333"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>结束日期</t>
+    </r>
   </si>
   <si>
     <r>
@@ -166,15 +188,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF333333"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9.75"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1121,10 +1143,10 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -1133,10 +1155,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
     </row>

--- a/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
+++ b/erp-server/erp-server-plm/src/main/resources/excel/cfgMoldReturnTemplate.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <r>
       <rPr>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -104,6 +110,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -154,6 +166,43 @@
         <charset val="134"/>
       </rPr>
       <t>返还金额</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>通知类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多个请用英文逗号隔开</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Courier New"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
     </r>
   </si>
   <si>
@@ -173,7 +222,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -185,6 +234,12 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Courier New"/>
       <charset val="134"/>
     </font>
     <font>
@@ -342,6 +397,16 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -664,137 +729,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -805,6 +870,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="28.125" customWidth="1"/>
@@ -1128,12 +1196,13 @@
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="17.875" customWidth="1"/>
     <col min="7" max="7" width="20.125" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="18.125" customWidth="1"/>
+    <col min="8" max="8" width="37.625" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,6 +1230,9 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="2">
